--- a/analysis/data/annotation/[Archived] Labeling SDG 5 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 5 - Benchmarking Dataset.xlsx
@@ -72118,7 +72118,7 @@
     <row r="2">
       <c r="A2" s="16" t="str">
         <f t="shared" ref="A2:A70" si="1">LEFT(MD5(B2), 7)</f>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>161</v>
@@ -72140,7 +72140,7 @@
     <row r="3">
       <c r="A3" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>304</v>
@@ -72162,7 +72162,7 @@
     <row r="4">
       <c r="A4" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>297</v>
@@ -72187,7 +72187,7 @@
     <row r="5">
       <c r="A5" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>351</v>
@@ -72212,7 +72212,7 @@
     <row r="6">
       <c r="A6" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>182</v>
@@ -72234,7 +72234,7 @@
     <row r="7">
       <c r="A7" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>125</v>
@@ -72259,7 +72259,7 @@
     <row r="8">
       <c r="A8" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>268</v>
@@ -72281,7 +72281,7 @@
     <row r="9">
       <c r="A9" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>173</v>
@@ -72303,7 +72303,7 @@
     <row r="10">
       <c r="A10" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>96</v>
@@ -72325,7 +72325,7 @@
     <row r="11">
       <c r="A11" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>273</v>
@@ -72347,7 +72347,7 @@
     <row r="12">
       <c r="A12" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>357</v>
@@ -72369,7 +72369,7 @@
     <row r="13">
       <c r="A13" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>343</v>
@@ -72391,7 +72391,7 @@
     <row r="14">
       <c r="A14" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>523</v>
@@ -72416,7 +72416,7 @@
     <row r="15">
       <c r="A15" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>525</v>
@@ -72441,7 +72441,7 @@
     <row r="16">
       <c r="A16" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>233</v>
@@ -72463,7 +72463,7 @@
     <row r="17">
       <c r="A17" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>302</v>
@@ -72485,7 +72485,7 @@
     <row r="18">
       <c r="A18" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>253</v>
@@ -72507,7 +72507,7 @@
     <row r="19">
       <c r="A19" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>111</v>
@@ -72529,7 +72529,7 @@
     <row r="20">
       <c r="A20" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>105</v>
@@ -72551,7 +72551,7 @@
     <row r="21">
       <c r="A21" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>286</v>
@@ -72573,7 +72573,7 @@
     <row r="22">
       <c r="A22" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>90</v>
@@ -72595,7 +72595,7 @@
     <row r="23">
       <c r="A23" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>262</v>
@@ -72617,7 +72617,7 @@
     <row r="24">
       <c r="A24" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>245</v>
@@ -72639,7 +72639,7 @@
     <row r="25">
       <c r="A25" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>346</v>
@@ -72661,7 +72661,7 @@
     <row r="26">
       <c r="A26" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>200</v>
@@ -72683,7 +72683,7 @@
     <row r="27">
       <c r="A27" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>103</v>
@@ -72705,7 +72705,7 @@
     <row r="28">
       <c r="A28" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>191</v>
@@ -72727,7 +72727,7 @@
     <row r="29">
       <c r="A29" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>329</v>
@@ -72749,7 +72749,7 @@
     <row r="30">
       <c r="A30" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>527</v>
@@ -72774,7 +72774,7 @@
     <row r="31">
       <c r="A31" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>265</v>
@@ -72796,7 +72796,7 @@
     <row r="32">
       <c r="A32" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>255</v>
@@ -72818,7 +72818,7 @@
     <row r="33">
       <c r="A33" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>137</v>
@@ -72840,7 +72840,7 @@
     <row r="34">
       <c r="A34" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>299</v>
@@ -72862,7 +72862,7 @@
     <row r="35">
       <c r="A35" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>334</v>
@@ -72884,7 +72884,7 @@
     <row r="36">
       <c r="A36" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>529</v>
@@ -72909,7 +72909,7 @@
     <row r="37">
       <c r="A37" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>77</v>
@@ -72931,7 +72931,7 @@
     <row r="38">
       <c r="A38" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>80</v>
@@ -72953,7 +72953,7 @@
     <row r="39">
       <c r="A39" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>337</v>
@@ -72975,7 +72975,7 @@
     <row r="40">
       <c r="A40" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>314</v>
@@ -72997,7 +72997,7 @@
     <row r="41">
       <c r="A41" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>236</v>
@@ -73019,7 +73019,7 @@
     <row r="42">
       <c r="A42" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>128</v>
@@ -73041,7 +73041,7 @@
     <row r="43">
       <c r="A43" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>326</v>
@@ -73063,7 +73063,7 @@
     <row r="44">
       <c r="A44" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>213</v>
@@ -73085,7 +73085,7 @@
     <row r="45">
       <c r="A45" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>152</v>
@@ -73107,7 +73107,7 @@
     <row r="46">
       <c r="A46" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>283</v>
@@ -73129,7 +73129,7 @@
     <row r="47">
       <c r="A47" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>224</v>
@@ -73151,7 +73151,7 @@
     <row r="48">
       <c r="A48" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>349</v>
@@ -73173,7 +73173,7 @@
     <row r="49">
       <c r="A49" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>531</v>
@@ -73198,7 +73198,7 @@
     <row r="50">
       <c r="A50" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>321</v>
@@ -73220,7 +73220,7 @@
     <row r="51">
       <c r="A51" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>221</v>
@@ -73242,7 +73242,7 @@
     <row r="52">
       <c r="A52" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>533</v>
@@ -73267,7 +73267,7 @@
     <row r="53">
       <c r="A53" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>205</v>
@@ -73289,7 +73289,7 @@
     <row r="54">
       <c r="A54" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>143</v>
@@ -73311,7 +73311,7 @@
     <row r="55">
       <c r="A55" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>230</v>
@@ -73333,7 +73333,7 @@
     <row r="56">
       <c r="A56" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>211</v>
@@ -73355,7 +73355,7 @@
     <row r="57">
       <c r="A57" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>535</v>
@@ -73380,7 +73380,7 @@
     <row r="58">
       <c r="A58" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>309</v>
@@ -73402,7 +73402,7 @@
     <row r="59">
       <c r="A59" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>537</v>
@@ -73427,7 +73427,7 @@
     <row r="60">
       <c r="A60" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>539</v>
@@ -73452,7 +73452,7 @@
     <row r="61">
       <c r="A61" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>258</v>
@@ -73474,7 +73474,7 @@
     <row r="62">
       <c r="A62" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>247</v>
@@ -73496,7 +73496,7 @@
     <row r="63">
       <c r="A63" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>318</v>
@@ -73518,7 +73518,7 @@
     <row r="64">
       <c r="A64" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>188</v>
@@ -73540,7 +73540,7 @@
     <row r="65">
       <c r="A65" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>93</v>
@@ -73565,7 +73565,7 @@
     <row r="66">
       <c r="A66" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B66" s="16" t="s">
         <v>146</v>
@@ -73587,7 +73587,7 @@
     <row r="67">
       <c r="A67" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B67" s="16" t="s">
         <v>83</v>
@@ -73609,7 +73609,7 @@
     <row r="68">
       <c r="A68" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>540</v>
@@ -73634,7 +73634,7 @@
     <row r="69">
       <c r="A69" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B69" s="16" t="s">
         <v>87</v>
@@ -73656,7 +73656,7 @@
     <row r="70">
       <c r="A70" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
+        <v>Loading...</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>197</v>
